--- a/DirectX/Bin/Asset/Brotato/tables/Misc.xlsx
+++ b/DirectX/Bin/Asset/Brotato/tables/Misc.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\jglee\ASTR\AstrDX\DirectX\Bin\Asset\Brotato\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{8BFAD844-4E76-407C-9F24-B7C2C69B7739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6C4AC3-1B0A-4494-BCF9-B34D71CD09BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{682AACDC-2833-44C3-8C53-94BCF51E4CDF}"/>
   </bookViews>
@@ -1038,7 +1038,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>200</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>

--- a/DirectX/Bin/Asset/Brotato/tables/Misc.xlsx
+++ b/DirectX/Bin/Asset/Brotato/tables/Misc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\jglee\ASTR\AstrDX\DirectX\Bin\Asset\Brotato\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6C4AC3-1B0A-4494-BCF9-B34D71CD09BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D28057-DBA6-4818-AAA3-E57EBC3AF7BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{682AACDC-2833-44C3-8C53-94BCF51E4CDF}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>PotatoBodyTexPath</t>
   </si>
@@ -39,6 +39,101 @@
   <si>
     <t>ID</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>FruitTexPath</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemBoxTexPath</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>LegendaryItemBoxTexPath</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaterialTexPath0</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaterialTexPath1</t>
+  </si>
+  <si>
+    <t>MaterialTexPath2</t>
+  </si>
+  <si>
+    <t>MaterialTexPath3</t>
+  </si>
+  <si>
+    <t>MaterialTexPath4</t>
+  </si>
+  <si>
+    <t>MaterialTexPath5</t>
+  </si>
+  <si>
+    <t>MaterialTexPath6</t>
+  </si>
+  <si>
+    <t>MaterialTexPath7</t>
+  </si>
+  <si>
+    <t>MaterialTexPath8</t>
+  </si>
+  <si>
+    <t>MaterialTexPath9</t>
+  </si>
+  <si>
+    <t>MaterialTexPath10</t>
+  </si>
+  <si>
+    <t>MaterialTexPath11</t>
+  </si>
+  <si>
+    <t>items/consumables/fruit/fruit.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>items/consumables/item_box/item_box.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>items/consumables/legendary_item_box/legendary_item_box.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>items/materials/material_0000.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>items/materials/material_0001.png</t>
+  </si>
+  <si>
+    <t>items/materials/material_0002.png</t>
+  </si>
+  <si>
+    <t>items/materials/material_0003.png</t>
+  </si>
+  <si>
+    <t>items/materials/material_0004.png</t>
+  </si>
+  <si>
+    <t>items/materials/material_0005.png</t>
+  </si>
+  <si>
+    <t>items/materials/material_0006.png</t>
+  </si>
+  <si>
+    <t>items/materials/material_0007.png</t>
+  </si>
+  <si>
+    <t>items/materials/material_0008.png</t>
+  </si>
+  <si>
+    <t>items/materials/material_0009.png</t>
+  </si>
+  <si>
+    <t>items/materials/material_0010.png</t>
   </si>
 </sst>
 </file>
@@ -1010,10 +1105,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E256355-C333-4347-86B2-953E0FA04B37}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -1026,8 +1121,53 @@
       <c r="D1" t="s">
         <v>2</v>
       </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>18</v>
+      </c>
+      <c r="R1" t="s">
+        <v>19</v>
+      </c>
+      <c r="S1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1039,6 +1179,48 @@
       </c>
       <c r="D2">
         <v>500</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S2" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
